--- a/data/trans_bre/IP24_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 11,32</t>
+          <t>-7,45; 11,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 2,95</t>
+          <t>-15,37; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 14,14</t>
+          <t>-5,45; 14,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 5,57</t>
+          <t>-20,5; 7,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 17,44</t>
+          <t>-10,04; 17,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 5,05</t>
+          <t>-22,19; 4,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 26,92</t>
+          <t>-8,04; 26,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,08; 12,47</t>
+          <t>-34,67; 16,67</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 4,78</t>
+          <t>-6,56; 5,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,5</t>
+          <t>1,91; 10,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,88</t>
+          <t>-2,47; 7,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 13,27</t>
+          <t>-1,82; 13,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 25,81</t>
+          <t>-26,57; 30,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,46; 235,09</t>
+          <t>20,79; 242,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 63,03</t>
+          <t>-16,56; 76,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 102,12</t>
+          <t>-11,1; 107,13</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 8,69</t>
+          <t>-3,24; 8,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 6,48</t>
+          <t>-0,02; 6,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 8,17</t>
+          <t>-0,07; 7,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 5,75</t>
+          <t>-7,19; 4,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 124,86</t>
+          <t>-29,62; 119,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 1372,63</t>
+          <t>-33,04; 1388,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 375,78</t>
+          <t>-6,65; 304,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 60,24</t>
+          <t>-43,76; 45,28</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,88</t>
+          <t>1,57; 11,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 14,4</t>
+          <t>4,04; 14,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 14,04</t>
+          <t>2,79; 13,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 36,67</t>
+          <t>0,46; 33,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,75; 192,62</t>
+          <t>12,22; 211,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,38; 433,63</t>
+          <t>48,56; 418,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,18; 335,43</t>
+          <t>29,93; 351,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 303,99</t>
+          <t>-8,26; 265,1</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,31</t>
+          <t>-1,94; 5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,6</t>
+          <t>0,93; 7,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,27</t>
+          <t>1,64; 8,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 15,95</t>
+          <t>0,33; 17,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 24,81</t>
+          <t>-7,81; 25,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 53,47</t>
+          <t>5,04; 52,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 54,03</t>
+          <t>9,02; 58,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 101,24</t>
+          <t>0,54; 97,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 11,69</t>
+          <t>-7,33; 11,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 3,02</t>
+          <t>-15,68; 2,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 14,04</t>
+          <t>-4,47; 14,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 7,57</t>
+          <t>-23,52; 5,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 17,81</t>
+          <t>-9,87; 16,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 4,73</t>
+          <t>-22,6; 4,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 26,83</t>
+          <t>-7,39; 28,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 16,67</t>
+          <t>-39,6; 10,96</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 5,48</t>
+          <t>-6,81; 5,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 10,82</t>
+          <t>1,74; 10,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 7,72</t>
+          <t>-3,56; 6,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 13,33</t>
+          <t>-1,74; 13,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 30,68</t>
+          <t>-29,02; 26,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,79; 242,1</t>
+          <t>19,07; 243,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 76,27</t>
+          <t>-22,44; 60,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 107,13</t>
+          <t>-11,04; 101,85</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 8,54</t>
+          <t>-3,74; 8,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 6,18</t>
+          <t>0,41; 6,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 7,81</t>
+          <t>0,3; 8,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 4,76</t>
+          <t>-7,26; 5,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 119,73</t>
+          <t>-27,68; 117,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 1388,97</t>
+          <t>-6,6; 1289,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 304,32</t>
+          <t>-3,98; 355,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 45,28</t>
+          <t>-45,04; 54,35</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,64</t>
+          <t>1,53; 11,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 14,17</t>
+          <t>4,0; 14,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 13,68</t>
+          <t>2,49; 13,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 33,29</t>
+          <t>0,32; 37,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,22; 211,84</t>
+          <t>11,81; 213,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,56; 418,95</t>
+          <t>48,62; 419,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,93; 351,86</t>
+          <t>25,13; 308,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 265,1</t>
+          <t>-8,16; 279,36</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,5</t>
+          <t>-1,79; 5,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,64</t>
+          <t>0,89; 8,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,55</t>
+          <t>1,71; 8,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 17,93</t>
+          <t>-0,38; 15,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 25,93</t>
+          <t>-7,38; 26,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 52,72</t>
+          <t>4,57; 57,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,02; 58,78</t>
+          <t>8,73; 53,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 97,65</t>
+          <t>-2,37; 94,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-7,11</t>
+          <t>-10,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-13,57%</t>
+          <t>-19,48%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 11,41</t>
+          <t>-7,58; 11,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 2,61</t>
+          <t>-16,17; 2,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 14,86</t>
+          <t>-5,1; 14,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 5,08</t>
+          <t>-24,09; 3,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 16,94</t>
+          <t>-9,96; 17,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 4,58</t>
+          <t>-23,15; 5,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 28,38</t>
+          <t>-7,79; 26,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 10,96</t>
+          <t>-41,59; 6,41</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 5,02</t>
+          <t>-6,81; 4,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 10,54</t>
+          <t>1,72; 10,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 6,87</t>
+          <t>-3,02; 6,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 13,22</t>
+          <t>-3,63; 9,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 26,06</t>
+          <t>-27,34; 25,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,07; 243,55</t>
+          <t>16,46; 235,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 60,9</t>
+          <t>-19,51; 63,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 101,85</t>
+          <t>-21,11; 76,5</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-10,27%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 8,46</t>
+          <t>-3,5; 8,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,33</t>
+          <t>0,38; 6,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 8,47</t>
+          <t>0,16; 8,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 5,3</t>
+          <t>-5,65; 6,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 117,07</t>
+          <t>-29,99; 124,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1289,77</t>
+          <t>-22,43; 1372,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 355,72</t>
+          <t>-0,59; 375,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,04; 54,35</t>
+          <t>-38,42; 76,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,88</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 11,65</t>
+          <t>1,25; 10,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 14,22</t>
+          <t>3,96; 14,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 13,37</t>
+          <t>2,42; 14,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 37,61</t>
+          <t>-6,31; 8,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,81; 213,05</t>
+          <t>10,75; 192,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,62; 419,16</t>
+          <t>41,38; 433,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,13; 308,99</t>
+          <t>26,18; 335,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 279,36</t>
+          <t>-33,83; 84,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,75</t>
+          <t>-1,94; 5,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,03</t>
+          <t>1,23; 7,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,43</t>
+          <t>1,6; 8,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 15,96</t>
+          <t>-2,87; 5,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 26,22</t>
+          <t>-7,92; 24,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 57,12</t>
+          <t>7,25; 53,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 53,99</t>
+          <t>9,06; 54,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 94,45</t>
+          <t>-15,86; 36,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,62</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,37</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-10,19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-10,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-19,48%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.93272872650363</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6.624891338278505</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>4.374645888621886</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-10.19382388685992</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.02726810306575005</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1017492903779634</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.07459844823961891</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1947684192141252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,58; 11,32</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-16,17; 2,95</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,1; 14,14</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-24,09; 3,05</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-9,96; 17,44</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-23,15; 5,05</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-7,79; 26,92</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-41,59; 6,41</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.579190935693219</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-16.17422553269217</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.098636223560429</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-24.08788181083157</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.09959006214325648</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.231481117267682</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.07786152207074261</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4158691018401168</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.32352458333243</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.94558643830169</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>14.14407764457088</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.054333246985319</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1744250871162055</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.05047744302732969</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.2691892611812742</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.06413595643428147</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,94</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,97</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,79</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-4,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,81; 4,78</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 10,5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,02; 6,88</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; 9,33</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-27,34; 25,81</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,46; 235,09</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-19,51; 63,03</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-21,11; 76,5</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.8927691923647313</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.944283353576314</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.966193811060515</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2.792941579082317</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.04166660808489999</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.9812894310010185</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1466011083353368</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1854699094437387</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,96</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>231,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.806943939821138</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.720533025167332</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.020567970477172</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.630496218807337</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2733884604039194</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.1645799387515746</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.195129741914822</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2111093937279044</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 8,69</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 6,48</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,16; 8,17</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,65; 6,79</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-29,99; 124,86</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-22,43; 1372,63</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-0,59; 375,78</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-38,42; 76,95</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.779731389107263</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.49871384602609</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.876306138959324</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>9.33190218671853</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2581321892551381</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.350942764161422</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.6303499552565719</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.765011990234701</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,35</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9,02</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,81</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,51</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>167,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>123,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.606935698899573</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.910603497011088</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.961312117226171</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.02134516459961627</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2691774873919989</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2.310474080699696</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.9907865227874694</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.001740851924630502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 10,88</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3,96; 14,4</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2,42; 14,04</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,31; 8,99</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,75; 192,62</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41,38; 433,63</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,18; 335,43</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-33,83; 84,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.504095478031051</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3795909008905468</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1611352435948984</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.650791591537963</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.299942085902039</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2242821330011935</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.005934438359489582</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3841519347228217</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.693230052782706</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.478842121446972</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.166680133298927</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.789601830271772</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.248550778623061</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>13.7262530794108</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3.757791136513872</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.7695247612240171</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6.347930272973766</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>9.018739926507783</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>7.812954021383903</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.507846641824352</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.8319368362332318</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.669988761742934</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1.234020812874435</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1747383103556086</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.249118682672094</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3.960313296598364</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2.418724582757934</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.30975337450661</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.1075263505078455</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.4138130808825679</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.2618323563251058</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.338253142311282</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.8765028205768</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>14.40090594781948</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>14.03899176667132</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>8.991125137513603</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.926208708378055</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>4.336292891301067</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>3.354314571135059</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.8453910119776601</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,38</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>27,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,94; 5,31</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 7,6</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 8,27</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,87; 5,35</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-7,92; 24,81</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,25; 53,47</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,06; 54,03</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-15,86; 36,06</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.88328907217443</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4.383816075541716</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.158983543142718</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.318541741127788</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.08044540443068166</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2749764974685549</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.3071041157382747</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.07970267222862448</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.941612367670936</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.228792136231546</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.600244214485234</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.865012993804087</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.07917703744726061</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.07247867375259745</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.09056376903349926</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1585717889975327</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.311134242741181</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.596844932496532</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8.271142472386536</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.347693895098334</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2480542128992607</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.5347135597567968</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.5402743767416384</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3606103638541471</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
